--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4F7E93-0698-4858-8EDA-77928EE43F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486D73D2-7C67-4118-831A-320D1441B89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="804">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -3316,12 +3316,12 @@
       <c r="I2" s="19"/>
       <c r="J2" s="11">
         <f>SUM(I3:I560)</f>
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="12">
         <f>H2-J2</f>
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3431,18 +3431,20 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="37">
         <v>11</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="54" t="s">
         <v>550</v>
       </c>
       <c r="G6" s="21">
@@ -3452,7 +3454,7 @@
       <c r="H6" s="22"/>
       <c r="I6" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="24"/>
       <c r="K6" s="25"/>
@@ -3467,18 +3469,20 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="37">
         <v>13.5</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="54" t="s">
         <v>551</v>
       </c>
       <c r="G7" s="21">
@@ -3488,7 +3492,7 @@
       <c r="H7" s="22"/>
       <c r="I7" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="24"/>
       <c r="K7" s="25"/>
@@ -3503,18 +3507,20 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="37">
         <v>12</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="54" t="s">
         <v>553</v>
       </c>
       <c r="G8" s="21">
@@ -3524,7 +3530,7 @@
       <c r="H8" s="22"/>
       <c r="I8" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="24"/>
       <c r="K8" s="25"/>
@@ -3575,18 +3581,20 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="B10" s="67"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="37">
         <v>29</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="54" t="s">
         <v>555</v>
       </c>
       <c r="G10" s="21">
@@ -3596,25 +3604,27 @@
       <c r="H10" s="22"/>
       <c r="I10" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="24"/>
       <c r="K10" s="25"/>
       <c r="L10" s="24"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E11" s="70">
+      <c r="E11" s="37">
         <v>15</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="54" t="s">
         <v>556</v>
       </c>
       <c r="G11" s="21">
@@ -3624,7 +3634,7 @@
       <c r="H11" s="22"/>
       <c r="I11" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="24"/>
       <c r="K11" s="25"/>
@@ -3639,18 +3649,20 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="37">
         <v>129</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="54" t="s">
         <v>557</v>
       </c>
       <c r="G12" s="21">
@@ -3660,7 +3672,7 @@
       <c r="H12" s="22"/>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="24"/>
       <c r="K12" s="25"/>
@@ -17860,20 +17872,20 @@
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A447" s="33" t="s">
+      <c r="A447" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="B447" s="34" t="s">
-        <v>523</v>
-      </c>
-      <c r="C447" s="3"/>
-      <c r="D447" s="36" t="s">
+      <c r="B447" s="1"/>
+      <c r="C447" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D447" s="13" t="s">
         <v>803</v>
       </c>
-      <c r="E447" s="39">
+      <c r="E447" s="37">
         <v>9</v>
       </c>
-      <c r="F447" s="79" t="s">
+      <c r="F447" s="54" t="s">
         <v>796</v>
       </c>
       <c r="G447" s="21">
@@ -17883,7 +17895,7 @@
       <c r="H447" s="22"/>
       <c r="I447" s="23">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J447" s="24"/>
       <c r="K447" s="25"/>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486D73D2-7C67-4118-831A-320D1441B89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48B97F0-B039-46DC-BD2C-E389CA27AE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="804">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -3316,12 +3316,12 @@
       <c r="I2" s="19"/>
       <c r="J2" s="11">
         <f>SUM(I3:I560)</f>
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="12">
         <f>H2-J2</f>
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -4351,16 +4351,18 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="14" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>569</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="53" t="s">
+      <c r="E33" s="37"/>
+      <c r="F33" s="54" t="s">
         <v>568</v>
       </c>
       <c r="G33" s="21">
@@ -4370,7 +4372,7 @@
       <c r="H33" s="22"/>
       <c r="I33" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="24"/>
       <c r="K33" s="25"/>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA76F764-D38B-4EF2-9307-469812AAA476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC580E4-4E76-42E1-98C0-FE02B127B2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="804">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -2451,6 +2451,9 @@
   </si>
   <si>
     <t>FIPHI (A voir si pas à la maison)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/fr/release/1417628-Bar-Kays-Flying-High-On-Your-Love</t>
   </si>
 </sst>
 </file>
@@ -2900,6 +2903,20 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2930,20 +2947,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3246,31 +3249,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="82" t="s">
+      <c r="B1" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="86" t="s">
         <v>304</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="E1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="82" t="s">
         <v>547</v>
       </c>
-      <c r="G1" s="87" t="s">
+      <c r="G1" s="77" t="s">
         <v>266</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="I1" s="84"/>
+      <c r="I1" s="74"/>
       <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
@@ -3280,18 +3283,18 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="75"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="88"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="78"/>
       <c r="H2" s="10">
         <f>SUM(G3:G560)</f>
         <v>504</v>
       </c>
-      <c r="I2" s="85"/>
+      <c r="I2" s="75"/>
       <c r="J2" s="11">
         <f>SUM(I3:I560)</f>
         <v>300</v>
@@ -4649,7 +4652,7 @@
       </c>
       <c r="E43" s="31"/>
       <c r="F43" s="46" t="s">
-        <v>577</v>
+        <v>803</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" si="2"/>
@@ -7749,7 +7752,7 @@
       </c>
       <c r="H137" s="18"/>
       <c r="I137" s="19">
-        <f t="shared" ref="I135:I199" si="12">COUNTA(C137)</f>
+        <f t="shared" ref="I137:I199" si="12">COUNTA(C137)</f>
         <v>0</v>
       </c>
       <c r="J137" s="19"/>
@@ -19959,9 +19962,9 @@
       <c r="D511" s="53"/>
       <c r="E511" s="55"/>
       <c r="F511" s="58"/>
-      <c r="G511" s="89"/>
+      <c r="G511" s="79"/>
       <c r="H511" s="24"/>
-      <c r="I511" s="86"/>
+      <c r="I511" s="76"/>
       <c r="J511" s="24"/>
       <c r="K511" s="24"/>
       <c r="L511" s="24"/>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC580E4-4E76-42E1-98C0-FE02B127B2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6648E39D-94C7-4F4C-9C33-9ABECC858C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="804">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -3297,12 +3297,12 @@
       <c r="I2" s="75"/>
       <c r="J2" s="11">
         <f>SUM(I3:I560)</f>
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="12">
         <f>H2-J2</f>
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -8024,16 +8024,18 @@
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B146" s="21"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="14" t="s">
+      <c r="B146" s="1"/>
+      <c r="C146" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" s="13" t="s">
         <v>627</v>
       </c>
-      <c r="E146" s="31"/>
-      <c r="F146" s="46" t="s">
+      <c r="E146" s="30"/>
+      <c r="F146" s="47" t="s">
         <v>626</v>
       </c>
       <c r="G146" s="20">
@@ -8043,7 +8045,7 @@
       <c r="H146" s="18"/>
       <c r="I146" s="19">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="19"/>
       <c r="K146" s="20"/>
